--- a/www/download/IND.surplus_value.empe.r.pc.rpO1.xlsx
+++ b/www/download/IND.surplus_value.empe.r.pc.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>294.96</t>
+          <t>2.94961087668958</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>347.95</t>
+          <t>3.47952507938073</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>334.61</t>
+          <t>3.34610373886014</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>323.28</t>
+          <t>3.23284182770407</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612085</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612085</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.34948286612085</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>3.48247715311886</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>3.3494821684171</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3.2372772660396</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2.9497549327653</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
